--- a/Design/config/BattleUnitConfig.xlsx
+++ b/Design/config/BattleUnitConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$C$5</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="62">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -42,10 +42,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>攻击力</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>生命</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -141,31 +137,127 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>BulletExplosionFire</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>远程小兵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否隐藏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsShadow</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>模型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnitBing2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnitBing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>法术场</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnitSpell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnitHero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>关羽影子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SwordHitYellowCritical</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SoldierAtkRate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>士兵加成攻击系数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>士兵加成hp系数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SoldierHpRate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>.65</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>.8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Atk</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BulletExplosionFire</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>远程小兵</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否隐藏</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsShadow</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Def</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -173,79 +265,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>模型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Model</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitBing2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitBing</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>法术场</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitSpell</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitHero</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>关羽影子</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SwordHitYellowCritical</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SoldierAtkRate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>士兵加成攻击系数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>士兵加成hp系数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SoldierHpRate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>.65</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>.8</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -653,17 +673,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
     <col min="3" max="3" width="9.875" customWidth="1"/>
-    <col min="4" max="4" width="9.5" customWidth="1"/>
-    <col min="13" max="13" width="10.875" customWidth="1"/>
+    <col min="14" max="14" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -677,271 +696,295 @@
         <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="E2" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="J2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" s="5" t="s">
+      <c r="N2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="H4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="J4" s="5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>500001</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>130</v>
       </c>
       <c r="E5">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="F5">
+        <v>50</v>
+      </c>
+      <c r="G5">
         <v>10</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>12</v>
       </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7" t="s">
-        <v>50</v>
-      </c>
+      <c r="J5" s="7"/>
       <c r="K5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="N5" t="s">
-        <v>28</v>
+        <v>40</v>
+      </c>
+      <c r="O5" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>500002</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="E6">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F6">
+        <v>50</v>
+      </c>
+      <c r="G6">
         <v>7</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>35</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>15</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="M6" t="s">
-        <v>41</v>
+        <v>54</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="N6" t="s">
-        <v>31</v>
+        <v>39</v>
+      </c>
+      <c r="O6" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>501001</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
+      <c r="D7">
+        <v>9999</v>
+      </c>
       <c r="E7">
-        <v>9999</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="7"/>
+        <v>99</v>
+      </c>
+      <c r="F7">
+        <v>99</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="K7" s="7"/>
-      <c r="M7" t="s">
-        <v>44</v>
+      <c r="L7" s="7"/>
+      <c r="N7" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>501002</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -950,23 +993,26 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F8">
+        <v>50</v>
+      </c>
+      <c r="G8">
         <v>10</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>17</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
+        <v>43</v>
+      </c>
+      <c r="O8" t="s">
         <v>45</v>
-      </c>
-      <c r="N8" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D5">
+  <autoFilter ref="A4:C5">
     <sortState ref="A5:Q116">
       <sortCondition ref="A4:A72"/>
     </sortState>

--- a/Design/config/BattleUnitConfig.xlsx
+++ b/Design/config/BattleUnitConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -46,26 +46,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>移动速度</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击距离</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>导弹速度</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>技能</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>hit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -78,26 +62,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>MoveSpeed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Range</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MissileSpeed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Skills</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>HitEffect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -107,10 +75,6 @@
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>int[]</t>
@@ -125,39 +89,67 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>小兵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>远程小兵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否隐藏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsShadow</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>cs</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SwordHitBlue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>小兵</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BulletExplosionFire</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>远程小兵</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否隐藏</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsShadow</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>true</t>
+    <t>模型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnitBing2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnitBing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>法术场</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnitSpell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnitHero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>关羽影子</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -165,43 +157,55 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>模型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Model</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitBing2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitBing</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>法术场</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitSpell</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitHero</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>关羽影子</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SwordHitYellowCritical</t>
+    <t>float</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SoldierAtkRate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>士兵加成攻击系数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>士兵加成hp系数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SoldierHpRate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>.65</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>.8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atk</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Def</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -209,59 +213,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>float</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SoldierAtkRate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>士兵加成攻击系数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>士兵加成hp系数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SoldierHpRate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>.65</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>.8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Atk</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Def</t>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArmsId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArmsId</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -673,16 +637,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="3" max="3" width="9.875" customWidth="1"/>
-    <col min="14" max="14" width="10.875" customWidth="1"/>
+    <col min="3" max="4" width="9.875" customWidth="1"/>
+    <col min="12" max="12" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -692,323 +656,269 @@
       <c r="C1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="L1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>500001</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
+        <v>201</v>
+      </c>
+      <c r="E5">
         <v>130</v>
-      </c>
-      <c r="E5">
-        <v>50</v>
       </c>
       <c r="F5">
         <v>50</v>
       </c>
       <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" t="s">
-        <v>40</v>
-      </c>
-      <c r="O5" t="s">
-        <v>27</v>
+        <v>50</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>500002</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
+        <v>201</v>
+      </c>
+      <c r="E6">
         <v>90</v>
-      </c>
-      <c r="E6">
-        <v>50</v>
       </c>
       <c r="F6">
         <v>50</v>
       </c>
       <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>35</v>
-      </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="N6" t="s">
-        <v>39</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
+        <v>50</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>501001</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
+        <v>201</v>
+      </c>
+      <c r="E7">
         <v>9999</v>
-      </c>
-      <c r="E7">
-        <v>99</v>
       </c>
       <c r="F7">
         <v>99</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="N7" t="s">
-        <v>42</v>
+      <c r="G7">
+        <v>99</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="L7" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>501002</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
+        <v>201</v>
+      </c>
+      <c r="E8">
         <v>2</v>
-      </c>
-      <c r="E8">
-        <v>50</v>
       </c>
       <c r="F8">
         <v>50</v>
       </c>
       <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>17</v>
-      </c>
-      <c r="N8" t="s">
-        <v>43</v>
-      </c>
-      <c r="O8" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="L8" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
